--- a/data/trans_dic/IP16A05-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,64</t>
+          <t>0,0; 20,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,43</t>
+          <t>0,0; 22,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 39,06</t>
+          <t>4,81; 41,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 25,28</t>
+          <t>4,6; 25,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 24,37</t>
+          <t>2,81; 24,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,48; 34,11</t>
+          <t>6,48; 36,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,64</t>
+          <t>0,0; 26,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,5</t>
+          <t>0,0; 20,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 16,39</t>
+          <t>1,7; 16,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 24,06</t>
+          <t>5,04; 23,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 24,34</t>
+          <t>6,06; 26,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 17,32</t>
+          <t>3,85; 17,45</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 27,32</t>
+          <t>3,12; 24,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,11; 46,06</t>
+          <t>15,73; 46,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,97</t>
+          <t>0,0; 13,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,19; 40,08</t>
+          <t>8,25; 40,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,27</t>
+          <t>0,0; 33,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 32,75</t>
+          <t>3,76; 32,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,58</t>
+          <t>0,0; 21,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 26,52</t>
+          <t>7,98; 27,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,02; 36,02</t>
+          <t>11,65; 34,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 20,92</t>
+          <t>2,4; 21,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 12,95</t>
+          <t>0,89; 12,7</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 52,45</t>
+          <t>6,46; 50,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 57,11</t>
+          <t>7,64; 57,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 27,71</t>
+          <t>3,04; 27,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 40,52</t>
+          <t>5,64; 45,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,67</t>
+          <t>0,0; 20,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 18,97</t>
+          <t>2,14; 18,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,16; 37,27</t>
+          <t>9,99; 36,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 28,96</t>
+          <t>3,49; 28,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,58</t>
+          <t>0,0; 14,93</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 25,15</t>
+          <t>6,96; 26,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 30,63</t>
+          <t>11,91; 29,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 20,05</t>
+          <t>6,09; 20,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 25,56</t>
+          <t>2,98; 24,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 25,14</t>
+          <t>7,05; 25,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 22,09</t>
+          <t>6,49; 21,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 20,21</t>
+          <t>3,59; 19,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 13,9</t>
+          <t>1,9; 14,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,75; 21,86</t>
+          <t>8,62; 22,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,53; 22,18</t>
+          <t>10,58; 22,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 16,79</t>
+          <t>5,8; 16,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 16,66</t>
+          <t>3,98; 16,87</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 24,04</t>
+          <t>2,76; 27,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 25,98</t>
+          <t>4,9; 27,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 23,53</t>
+          <t>2,29; 24,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,02</t>
+          <t>0,0; 6,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,65</t>
+          <t>0,0; 12,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 28,02</t>
+          <t>5,13; 28,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,52; 37,88</t>
+          <t>11,09; 40,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,3</t>
+          <t>0,0; 13,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 13,35</t>
+          <t>1,4; 12,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 22,36</t>
+          <t>6,52; 21,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,38; 27,15</t>
+          <t>8,46; 25,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 7,44</t>
+          <t>0,56; 7,29</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,48</t>
+          <t>0,0; 43,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,32</t>
+          <t>0,0; 22,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,61; 42,47</t>
+          <t>4,83; 41,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,89</t>
+          <t>0,0; 29,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,77</t>
+          <t>0,0; 38,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,33</t>
+          <t>0,0; 28,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 27,5</t>
+          <t>2,97; 24,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,43; 21,91</t>
+          <t>2,41; 20,77</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,41; 26,49</t>
+          <t>4,56; 24,54</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 14,14</t>
+          <t>5,44; 14,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,82; 23,72</t>
+          <t>13,04; 24,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,89; 16,11</t>
+          <t>7,2; 16,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,73; 14,11</t>
+          <t>4,45; 14,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 16,25</t>
+          <t>6,77; 15,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,74; 18,28</t>
+          <t>8,91; 18,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,08; 18,76</t>
+          <t>8,27; 18,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 9,3</t>
+          <t>3,12; 9,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,26; 13,57</t>
+          <t>7,08; 13,25</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,26; 19,36</t>
+          <t>12,27; 19,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,89; 15,53</t>
+          <t>8,99; 15,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,81; 10,63</t>
+          <t>4,78; 10,56</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1501</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2810</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3068</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3834</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1902</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2587</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4428</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4970</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3108</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4634</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>762; 6623</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1143; 6417</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>602; 5314</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1424; 8062</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4773</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6317</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>624; 5883</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2160; 9892</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2036; 8749</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2163; 9815</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6600</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3888</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2818</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5844</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7440</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2818</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>606; 4754</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3602; 10732</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3145</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1472; 7293</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3998</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>716; 6108</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5075</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2977; 10163</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>4075; 12058</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>745; 6542</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>417; 5961</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2840</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2132</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1098</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4971</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1098</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>741; 5828</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>676; 5101</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>667; 6091</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>704; 5643</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3493</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>706; 6248</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2392; 8703</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>666; 5537</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4016</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5405</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9659</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5332</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8256</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5528</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7538</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3186</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3548</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>10934</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17196</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8518</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>11804</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2622; 9823</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>5795; 14448</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2831; 9675</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2273; 18517</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2735; 9786</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3825; 12891</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1239; 6860</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1059; 8196</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>6594; 16884</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>11377; 23841</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4696; 13622</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>5264; 22306</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3695</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2573</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3630</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5924</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>7325</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8496</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>521; 5195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1404; 7871</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>609; 6518</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1784</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3057</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1408; 7721</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2845; 10435</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4776</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>599; 5473</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3654; 12094</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4422; 13313</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>362; 4730</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2338</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1209</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1773</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3035</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2896</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>590; 5118</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4125</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3744</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4341</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>619; 5106</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>549; 4737</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1254; 6754</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>9794</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>25063</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>13761</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>15013</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>19313</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>14755</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>9798</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>24476</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>44376</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>28516</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>24812</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>5968; 15495</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>18215; 33639</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>8838; 19797</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>7802; 24974</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>9162; 21161</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>13066; 27429</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9682; 21537</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>5593; 16375</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>17355; 32469</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>35131; 55455</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>21567; 37352</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>16964; 37441</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A05-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,48</t>
+          <t>0,0; 17,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,15</t>
+          <t>0,0; 22,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 41,81</t>
+          <t>4,71; 41,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 25,82</t>
+          <t>4,3; 25,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 24,76</t>
+          <t>2,77; 23,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,48; 36,68</t>
+          <t>6,63; 34,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,9</t>
+          <t>0,0; 27,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,12</t>
+          <t>0,0; 21,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 16,06</t>
+          <t>1,76; 16,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 23,06</t>
+          <t>5,9; 22,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 26,05</t>
+          <t>6,04; 25,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 17,45</t>
+          <t>4,02; 18,0</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 24,47</t>
+          <t>3,11; 26,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,73; 46,86</t>
+          <t>15,53; 45,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,42</t>
+          <t>0,0; 13,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,25; 40,84</t>
+          <t>8,2; 39,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,07</t>
+          <t>0,0; 27,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 32,04</t>
+          <t>3,75; 33,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,6</t>
+          <t>0,0; 21,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,98; 27,26</t>
+          <t>7,43; 28,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,65; 34,46</t>
+          <t>11,21; 34,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 21,06</t>
+          <t>2,3; 20,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 12,7</t>
+          <t>0,84; 12,68</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 50,81</t>
+          <t>7,17; 53,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 57,66</t>
+          <t>8,0; 56,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 27,75</t>
+          <t>3,16; 27,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 45,22</t>
+          <t>5,58; 40,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,19</t>
+          <t>0,0; 23,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 18,9</t>
+          <t>2,05; 18,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,99; 36,34</t>
+          <t>8,98; 35,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 28,97</t>
+          <t>3,31; 29,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,93</t>
+          <t>0,0; 14,3</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 26,07</t>
+          <t>7,24; 25,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,91; 29,7</t>
+          <t>11,76; 30,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 20,81</t>
+          <t>5,05; 20,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 24,24</t>
+          <t>3,05; 25,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 25,23</t>
+          <t>6,94; 25,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 21,88</t>
+          <t>6,98; 21,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 19,87</t>
+          <t>3,55; 20,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 14,68</t>
+          <t>1,84; 13,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,62; 22,08</t>
+          <t>8,74; 22,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,58; 22,17</t>
+          <t>10,56; 22,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 16,81</t>
+          <t>5,99; 17,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 16,87</t>
+          <t>3,56; 17,1</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 27,55</t>
+          <t>2,67; 23,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 27,48</t>
+          <t>5,03; 26,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 24,48</t>
+          <t>2,26; 21,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,17</t>
+          <t>0,0; 7,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,79</t>
+          <t>0,0; 10,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,13; 28,15</t>
+          <t>4,94; 25,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,09; 40,66</t>
+          <t>11,42; 40,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,27</t>
+          <t>0,0; 11,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,8</t>
+          <t>1,41; 14,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 21,57</t>
+          <t>6,56; 21,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,46; 25,46</t>
+          <t>9,05; 26,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 7,29</t>
+          <t>0,59; 8,71</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,01</t>
+          <t>0,0; 42,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,23</t>
+          <t>0,0; 23,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,83; 41,88</t>
+          <t>4,77; 39,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,9</t>
+          <t>0,0; 29,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,29</t>
+          <t>0,0; 39,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,37</t>
+          <t>0,0; 27,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,97; 24,49</t>
+          <t>3,04; 26,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 20,77</t>
+          <t>2,44; 19,22</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,56; 24,54</t>
+          <t>3,41; 25,91</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,44; 14,12</t>
+          <t>5,19; 13,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,04; 24,09</t>
+          <t>13,01; 23,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,2; 16,12</t>
+          <t>7,31; 16,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 14,24</t>
+          <t>4,49; 14,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,77; 15,64</t>
+          <t>7,18; 15,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,91; 18,7</t>
+          <t>8,87; 18,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,27; 18,4</t>
+          <t>8,3; 18,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,13</t>
+          <t>2,95; 9,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 13,25</t>
+          <t>7,3; 13,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,27; 19,37</t>
+          <t>12,3; 19,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,99; 15,57</t>
+          <t>8,58; 15,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,78; 10,56</t>
+          <t>4,32; 10,68</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3108</t>
+          <t>0; 2657</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4634</t>
+          <t>0; 4648</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>762; 6623</t>
+          <t>747; 6508</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1143; 6417</t>
+          <t>1069; 6394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>602; 5314</t>
+          <t>594; 5137</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1424; 8062</t>
+          <t>1456; 7604</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4773</t>
+          <t>0; 4916</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6317</t>
+          <t>0; 6797</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>624; 5883</t>
+          <t>645; 6021</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2160; 9892</t>
+          <t>2530; 9791</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2036; 8749</t>
+          <t>2030; 8569</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2163; 9815</t>
+          <t>2263; 10125</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>606; 4754</t>
+          <t>605; 5186</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3602; 10732</t>
+          <t>3557; 10350</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,47 +2150,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3145</t>
+          <t>0; 3256</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1472; 7293</t>
+          <t>1465; 7020</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3998</t>
+          <t>0; 3266</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>716; 6108</t>
+          <t>716; 6457</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5075</t>
+          <t>0; 4998</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2977; 10163</t>
+          <t>2771; 10561</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4075; 12058</t>
+          <t>3923; 12160</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>745; 6542</t>
+          <t>714; 6275</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>417; 5961</t>
+          <t>392; 5952</t>
         </is>
       </c>
     </row>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>741; 5828</t>
+          <t>822; 6179</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>676; 5101</t>
+          <t>707; 5029</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>667; 6091</t>
+          <t>694; 5950</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>704; 5643</t>
+          <t>697; 5039</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3493</t>
+          <t>0; 4032</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>706; 6248</t>
+          <t>679; 6048</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2392; 8703</t>
+          <t>2150; 8521</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>666; 5537</t>
+          <t>633; 5654</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4016</t>
+          <t>0; 3845</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2622; 9823</t>
+          <t>2728; 9691</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5795; 14448</t>
+          <t>5722; 14888</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2831; 9675</t>
+          <t>2347; 9465</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2273; 18517</t>
+          <t>2331; 19348</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2735; 9786</t>
+          <t>2692; 9902</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3825; 12891</t>
+          <t>4114; 12731</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1239; 6860</t>
+          <t>1227; 7182</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1059; 8196</t>
+          <t>1025; 7577</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6594; 16884</t>
+          <t>6687; 17101</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11377; 23841</t>
+          <t>11360; 23900</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4696; 13622</t>
+          <t>4855; 14036</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5264; 22306</t>
+          <t>4707; 22611</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>521; 5195</t>
+          <t>504; 4492</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1404; 7871</t>
+          <t>1440; 7717</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>609; 6518</t>
+          <t>602; 5855</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1784</t>
+          <t>0; 2024</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3057</t>
+          <t>0; 2491</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1408; 7721</t>
+          <t>1356; 7009</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2845; 10435</t>
+          <t>2930; 10461</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4776</t>
+          <t>0; 4068</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>599; 5473</t>
+          <t>601; 6043</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3654; 12094</t>
+          <t>3676; 12262</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4422; 13313</t>
+          <t>4730; 14044</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>362; 4730</t>
+          <t>382; 5648</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3035</t>
+          <t>0; 3032</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2896</t>
+          <t>0; 3004</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>590; 5118</t>
+          <t>583; 4848</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4125</t>
+          <t>0; 4115</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3744</t>
+          <t>0; 3880</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4341</t>
+          <t>0; 4229</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>619; 5106</t>
+          <t>633; 5572</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>549; 4737</t>
+          <t>555; 4382</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1254; 6754</t>
+          <t>940; 7130</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5968; 15495</t>
+          <t>5696; 15320</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18215; 33639</t>
+          <t>18169; 32549</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8838; 19797</t>
+          <t>8983; 19810</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7802; 24974</t>
+          <t>7875; 26025</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9162; 21161</t>
+          <t>9719; 21115</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13066; 27429</t>
+          <t>13008; 27172</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9682; 21537</t>
+          <t>9715; 22006</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5593; 16375</t>
+          <t>5287; 16464</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17355; 32469</t>
+          <t>17882; 32954</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35131; 55455</t>
+          <t>35215; 55742</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21567; 37352</t>
+          <t>20572; 36468</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16964; 37441</t>
+          <t>15327; 37884</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A05-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A05-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,14%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17,45%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,12%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,13%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,17%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>17,73%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,52</t>
+          <t>2,8; 24,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,22</t>
+          <t>6,48; 34,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 41,08</t>
+          <t>0,0; 26,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 25,73</t>
+          <t>0,0; 20,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 23,93</t>
+          <t>0,0; 20,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 34,6</t>
+          <t>0,0; 22,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,7</t>
+          <t>4,74; 39,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,65</t>
+          <t>3,83; 23,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 16,44</t>
+          <t>1,78; 16,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 22,82</t>
+          <t>5,35; 24,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 25,51</t>
+          <t>5,44; 24,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,02; 18,0</t>
+          <t>3,88; 16,94</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21,78%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>10,07%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>28,82%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,78%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 26,69</t>
+          <t>8,19; 40,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,53; 45,19</t>
+          <t>0,0; 32,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>3,71; 32,75</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 18,87</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,16; 27,32</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,11; 46,06</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8,2; 39,31</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 27,02</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,75; 33,87</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,27</t>
+          <t>0,0; 13,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 28,32</t>
+          <t>7,34; 26,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 34,75</t>
+          <t>12,02; 36,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 20,2</t>
+          <t>2,31; 20,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 12,68</t>
+          <t>0,75; 12,56</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17,09%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>24,75%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>28,07%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>8,17%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>3,15; 27,71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5,63; 40,52</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>7,17; 53,87</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>8,0; 56,86</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 20,23</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>3,16; 27,11</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 40,38</t>
+          <t>7,93; 52,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>7,3; 57,11</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 23,31</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 18,29</t>
+          <t>2,06; 18,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,98; 35,58</t>
+          <t>9,16; 37,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 29,58</t>
+          <t>3,53; 28,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,3</t>
+          <t>0,0; 13,9</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,23%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>14,34%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>19,86%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11,47%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 25,72</t>
+          <t>6,86; 25,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,76; 30,61</t>
+          <t>6,67; 22,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 20,36</t>
+          <t>3,55; 20,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 25,33</t>
+          <t>2,2; 14,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 25,53</t>
+          <t>6,93; 25,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 21,61</t>
+          <t>11,93; 30,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 20,8</t>
+          <t>6,0; 20,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 13,57</t>
+          <t>6,6; 24,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,74; 22,36</t>
+          <t>8,75; 21,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 22,22</t>
+          <t>10,53; 22,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,99; 17,33</t>
+          <t>5,88; 16,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 17,1</t>
+          <t>5,47; 16,32</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23,08%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>9,58%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>12,9%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>9,66%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>23,08%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,67; 23,83</t>
+          <t>0,0; 10,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 26,94</t>
+          <t>5,35; 28,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 21,99</t>
+          <t>11,52; 37,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,0; 10,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,42</t>
+          <t>2,74; 24,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 25,55</t>
+          <t>4,93; 25,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,42; 40,76</t>
+          <t>3,16; 23,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,31</t>
+          <t>0,0; 6,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 14,13</t>
+          <t>1,38; 13,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 21,87</t>
+          <t>6,47; 22,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,05; 26,86</t>
+          <t>9,38; 27,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 8,71</t>
+          <t>0,55; 6,93</t>
         </is>
       </c>
     </row>
@@ -1354,44 +1354,44 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12,37%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>10,89%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19,13%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,37%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>10,11%</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,97</t>
+          <t>0,0; 33,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,06</t>
+          <t>0,0; 44,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,77; 39,67</t>
+          <t>0,0; 26,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,83</t>
+          <t>0,0; 52,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,68</t>
+          <t>0,0; 24,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,64</t>
+          <t>4,17; 39,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,04; 26,72</t>
+          <t>3,01; 27,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 19,22</t>
+          <t>2,43; 21,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,41; 25,91</t>
+          <t>4,47; 26,29</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10,85%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13,17%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12,61%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>8,92%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>17,95%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>11,2%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,85%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,19; 13,96</t>
+          <t>7,08; 16,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,01; 23,31</t>
+          <t>8,74; 18,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,31; 16,13</t>
+          <t>8,08; 18,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 14,84</t>
+          <t>2,79; 9,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,18; 15,61</t>
+          <t>5,48; 14,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,87; 18,52</t>
+          <t>12,82; 23,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,3; 18,8</t>
+          <t>6,89; 16,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,95; 9,18</t>
+          <t>5,62; 12,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,3; 13,45</t>
+          <t>7,26; 13,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12,3; 19,47</t>
+          <t>12,26; 19,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,58; 15,2</t>
+          <t>8,89; 15,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,68</t>
+          <t>4,68; 9,56</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
+          <t>Menores que consumieron medicamentos antibióticos (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3834</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1501</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2810</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3068</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3834</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1618</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4566</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2657</t>
+          <t>601; 5231</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4648</t>
+          <t>1423; 7496</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>747; 6508</t>
+          <t>0; 4727</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1069; 6394</t>
+          <t>0; 5816</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>594; 5137</t>
+          <t>0; 3131</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1456; 7604</t>
+          <t>0; 4693</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4916</t>
+          <t>751; 6188</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6797</t>
+          <t>942; 5902</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>645; 6021</t>
+          <t>654; 6003</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2530; 9791</t>
+          <t>2297; 10323</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2030; 8569</t>
+          <t>1826; 8176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2263; 10125</t>
+          <t>2075; 9059</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,62 +2067,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3888</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2818</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1956</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6600</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3888</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>839</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5844</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7440</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>2818</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5844</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>7440</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2818</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1839</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>605; 5186</t>
+          <t>1463; 7157</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3557; 10350</t>
+          <t>0; 3901</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>707; 6243</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4270</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>615; 5308</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3690; 10548</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3256</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1465; 7020</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3266</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>716; 6457</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4998</t>
+          <t>0; 3101</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2771; 10561</t>
+          <t>2738; 9888</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3923; 12160</t>
+          <t>4205; 12604</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>714; 6275</t>
+          <t>718; 6496</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>392; 5952</t>
+          <t>340; 5728</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,49 +2275,49 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2132</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2840</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2483</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2702</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1098</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>4971</t>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>908</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>692; 6083</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>702; 5056</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>822; 6179</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>707; 5029</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0; 3040</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>694; 5950</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>697; 5039</t>
+          <t>910; 6017</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>645; 5052</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4032</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>679; 6048</t>
+          <t>681; 6272</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2150; 8521</t>
+          <t>2194; 8926</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>633; 5654</t>
+          <t>675; 5536</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3845</t>
+          <t>0; 3412</t>
         </is>
       </c>
     </row>
@@ -2420,37 +2420,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5528</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7538</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3186</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3261</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5405</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9659</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5332</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8256</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5528</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7538</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11804</t>
+          <t>8937</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2728; 9691</t>
+          <t>2661; 9753</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5722; 14888</t>
+          <t>3932; 13011</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2347; 9465</t>
+          <t>1227; 6978</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2331; 19348</t>
+          <t>1096; 7457</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2692; 9902</t>
+          <t>2613; 9477</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4114; 12731</t>
+          <t>5801; 14898</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1227; 7182</t>
+          <t>2788; 9319</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1025; 7577</t>
+          <t>2807; 10443</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6687; 17101</t>
+          <t>6688; 16717</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11360; 23900</t>
+          <t>11327; 23859</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4855; 14036</t>
+          <t>4766; 13601</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4707; 22611</t>
+          <t>5045; 15059</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3630</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5924</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1806</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3695</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2573</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3630</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5924</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>340</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1528</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>504; 4492</t>
+          <t>0; 2545</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1440; 7717</t>
+          <t>1468; 7686</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>602; 5855</t>
+          <t>2957; 9720</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2024</t>
+          <t>0; 3397</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2491</t>
+          <t>516; 4532</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1356; 7009</t>
+          <t>1413; 7443</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2930; 10461</t>
+          <t>842; 6263</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4068</t>
+          <t>0; 1780</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>601; 6043</t>
+          <t>592; 5706</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3676; 12262</t>
+          <t>3629; 12536</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4730; 14044</t>
+          <t>4905; 14195</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>382; 5648</t>
+          <t>335; 4214</t>
         </is>
       </c>
     </row>
@@ -2836,37 +2836,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2904,44 +2904,44 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1209</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>769</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2338</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2172</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1209</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>2108</t>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3069</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3032</t>
+          <t>0; 4675</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3004</t>
+          <t>0; 4377</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>583; 4848</t>
+          <t>0; 3681</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4115</t>
+          <t>0; 3703</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3880</t>
+          <t>0; 3167</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4229</t>
+          <t>519; 4949</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>633; 5572</t>
+          <t>628; 5734</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>555; 4382</t>
+          <t>555; 4995</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>940; 7130</t>
+          <t>1186; 6984</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>19313</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>14755</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8934</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>9794</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>25063</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>13761</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>15013</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>14682</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>19313</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>14755</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>20846</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5696; 15320</t>
+          <t>9582; 21984</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18169; 32549</t>
+          <t>12819; 26815</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8983; 19810</t>
+          <t>9454; 21953</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7875; 26025</t>
+          <t>4527; 15079</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9719; 21115</t>
+          <t>6011; 15518</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13008; 27172</t>
+          <t>17896; 33115</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9715; 22006</t>
+          <t>8457; 19789</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5287; 16464</t>
+          <t>7914; 17836</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17882; 32954</t>
+          <t>17798; 33256</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35215; 55742</t>
+          <t>35107; 55431</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20572; 36468</t>
+          <t>21326; 37256</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15327; 37884</t>
+          <t>14197; 29003</t>
         </is>
       </c>
     </row>
